--- a/product_order_forms/017_retail_shelf_mirror_display_order_form--product_order_forms.xlsx
+++ b/product_order_forms/017_retail_shelf_mirror_display_order_form--product_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'type_a',_'value':_'type_a'}</t>
+          <t>type_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Type A', 'value': 'type_a'}</t>
+          <t>Type A</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'type_b',_'value':_'type_b'}</t>
+          <t>type_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Type B', 'value': 'type_b'}</t>
+          <t>Type B</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'type_c',_'value':_'type_c'}</t>
+          <t>type_c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Type C', 'value': 'type_c'}</t>
+          <t>Type C</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'mm/dd/yyyy',_'value':_'mmddyyyy'}</t>
+          <t>mm/dd/yyyy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'mm/dd/yyyy', 'value': 'mmddyyyy'}</t>
+          <t>mm/dd/yyyy</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'mm/dd/yy',_'value':_'mmddyy'}</t>
+          <t>mm/dd/yy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'mm/dd/yy', 'value': 'mmddyy'}</t>
+          <t>mm/dd/yy</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'mm/dd',_'value':_'mmd'}</t>
+          <t>mm/dd</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'mm/dd', 'value': 'mmd'}</t>
+          <t>mm/dd</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'yy-mm-dd',_'value':_'yy_mmd'}</t>
+          <t>yy-mm-dd</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'yy-mm-dd', 'value': 'yy_mmd'}</t>
+          <t>yy-mm-dd</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'open',_'value':_'open'}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Open', 'value': 'open'}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'closed',_'value':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Closed', 'value': 'closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
